--- a/input.xlsx
+++ b/input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pvk/Documents/GitHub/FEL3D/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD26B455-BC82-DD46-8E29-B4B81188E215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BE5FFA-348D-C744-A4FA-4E942DB51720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30320" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Z</t>
   </si>
@@ -94,12 +94,6 @@
     <t>Near gs?</t>
   </si>
   <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
     <t>Additional data</t>
   </si>
   <si>
@@ -110,6 +104,9 @@
   </si>
   <si>
     <t>p</t>
+  </si>
+  <si>
+    <t>0.2</t>
   </si>
 </sst>
 </file>
@@ -395,9 +392,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -435,7 +432,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -541,7 +538,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -683,7 +680,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -760,7 +757,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>8</v>
@@ -793,7 +790,7 @@
         <v>18</v>
       </c>
       <c r="T1" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="12" customFormat="1">
@@ -804,16 +801,16 @@
         <v>236</v>
       </c>
       <c r="C2" s="12">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="D2" s="13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>14</v>
@@ -824,11 +821,11 @@
       <c r="I2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="11" t="s">
-        <v>20</v>
+      <c r="J2" s="11">
+        <v>1</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
@@ -842,7 +839,7 @@
         <v>14</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:20">
